--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>127128259</v>
       </c>
       <c r="B3" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>127128256</v>
       </c>
       <c r="B4" t="n">
-        <v>57815</v>
+        <v>57819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>127128259</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>127128256</v>
       </c>
       <c r="B4" t="n">
-        <v>57819</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,6 +1032,1156 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127829735</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fulagylet, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>466358</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6254965</v>
+      </c>
+      <c r="S5" t="n">
+        <v>54</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127826639</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gripsvalla, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>466524</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6255148</v>
+      </c>
+      <c r="S6" t="n">
+        <v>59</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Muhr, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127829736</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fulagylet, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>466358</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6254965</v>
+      </c>
+      <c r="S7" t="n">
+        <v>54</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127831102</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fulagylet, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>466533</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6254716</v>
+      </c>
+      <c r="S8" t="n">
+        <v>59</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Muhr, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127826645</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96058</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gripsvalla, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>466524</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6255148</v>
+      </c>
+      <c r="S9" t="n">
+        <v>59</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Muhr, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127826634</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gripsvalla, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>466524</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6255148</v>
+      </c>
+      <c r="S10" t="n">
+        <v>59</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Muhr, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127831101</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fulagylet, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>466533</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6254716</v>
+      </c>
+      <c r="S11" t="n">
+        <v>59</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Muhr, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127826642</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gripsvalla, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>466524</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6255148</v>
+      </c>
+      <c r="S12" t="n">
+        <v>59</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Muhr, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127030122</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ost Fulagylet, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>466480</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6254981</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128043396</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57821</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fulagylet, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>466575</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6254862</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Muhr, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>127128259</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>127128256</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>57824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>127829735</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>127826639</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>127829736</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127831102</v>
       </c>
       <c r="B8" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>127826645</v>
       </c>
       <c r="B9" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127826634</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127831101</v>
       </c>
       <c r="B11" t="n">
-        <v>57821</v>
+        <v>57824</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127826642</v>
       </c>
       <c r="B12" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>127030122</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>128043396</v>
       </c>
       <c r="B14" t="n">
-        <v>57821</v>
+        <v>57824</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström</t>
+          <t>Thomas Arnström, Per Muhr</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>127128259</v>
       </c>
       <c r="B3" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>127128256</v>
       </c>
       <c r="B4" t="n">
-        <v>57824</v>
+        <v>57830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>127829735</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>127826639</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>127829736</v>
       </c>
       <c r="B7" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127831102</v>
       </c>
       <c r="B8" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>127826645</v>
       </c>
       <c r="B9" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127826634</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127831101</v>
       </c>
       <c r="B11" t="n">
-        <v>57824</v>
+        <v>57830</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127826642</v>
       </c>
       <c r="B12" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>127030122</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>128043396</v>
       </c>
       <c r="B14" t="n">
-        <v>57824</v>
+        <v>57830</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Thomas Arnström, Per Muhr</t>
+          <t>Per Muhr, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>127826645</v>
       </c>
       <c r="B9" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>127826645</v>
       </c>
       <c r="B9" t="n">
-        <v>96070</v>
+        <v>96071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>127826645</v>
       </c>
       <c r="B9" t="n">
-        <v>96071</v>
+        <v>96072</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>127829735</v>
       </c>
       <c r="B5" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>127826639</v>
       </c>
       <c r="B6" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>127829736</v>
       </c>
       <c r="B7" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127831102</v>
       </c>
       <c r="B8" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>127826645</v>
       </c>
       <c r="B9" t="n">
-        <v>96072</v>
+        <v>96080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127826634</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127831101</v>
       </c>
       <c r="B11" t="n">
-        <v>57830</v>
+        <v>57831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127826642</v>
       </c>
       <c r="B12" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>127030122</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>128043396</v>
       </c>
       <c r="B14" t="n">
-        <v>57830</v>
+        <v>57831</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>127829735</v>
       </c>
       <c r="B5" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>127826639</v>
       </c>
       <c r="B6" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>127829736</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127831102</v>
       </c>
       <c r="B8" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>127826645</v>
       </c>
       <c r="B9" t="n">
-        <v>96080</v>
+        <v>96173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127826634</v>
       </c>
       <c r="B10" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127831101</v>
       </c>
       <c r="B11" t="n">
-        <v>57831</v>
+        <v>57843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>127826642</v>
       </c>
       <c r="B12" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>127030122</v>
       </c>
       <c r="B13" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>128043396</v>
       </c>
       <c r="B14" t="n">
-        <v>57831</v>
+        <v>57843</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström</t>
+          <t>Thomas Arnström, Per Muhr</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -2177,7 +2177,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Thomas Arnström, Per Muhr</t>
+          <t>Per Muhr, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>127030122</v>
       </c>
       <c r="B13" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>128043396</v>
       </c>
       <c r="B14" t="n">
-        <v>57843</v>
+        <v>57847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,6 +2182,307 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129499979</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fulagylet, Fulagylet, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>466402</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6254794</v>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129501845</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58097</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fulagylet, Fulagylet, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>466512</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6254919</v>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129500120</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fulagylet, Fulagylet, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>466442</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6254782</v>
+      </c>
+      <c r="S17" t="n">
+        <v>100</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -2184,32 +2184,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129499979</v>
+        <v>129501845</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>58097</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466402</v>
+        <v>466512</v>
       </c>
       <c r="R15" t="n">
-        <v>6254794</v>
+        <v>6254919</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -2252,9 +2252,19 @@
           <t>2025-10-31</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,32 +2291,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129501845</v>
+        <v>129499979</v>
       </c>
       <c r="B16" t="n">
-        <v>58097</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466512</v>
+        <v>466402</v>
       </c>
       <c r="R16" t="n">
-        <v>6254919</v>
+        <v>6254794</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -2349,19 +2359,9 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -2184,32 +2184,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129501845</v>
+        <v>129499979</v>
       </c>
       <c r="B15" t="n">
-        <v>58097</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466512</v>
+        <v>466402</v>
       </c>
       <c r="R15" t="n">
-        <v>6254919</v>
+        <v>6254794</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -2252,19 +2252,9 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,32 +2281,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129499979</v>
+        <v>129501845</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>58097</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2326,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466402</v>
+        <v>466512</v>
       </c>
       <c r="R16" t="n">
-        <v>6254794</v>
+        <v>6254919</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -2359,9 +2349,19 @@
           <t>2025-10-31</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -2187,7 +2187,7 @@
         <v>129499979</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>129501845</v>
       </c>
       <c r="B16" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>129500120</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -2184,32 +2184,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129499979</v>
+        <v>129501845</v>
       </c>
       <c r="B15" t="n">
-        <v>57890</v>
+        <v>58105</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466402</v>
+        <v>466512</v>
       </c>
       <c r="R15" t="n">
-        <v>6254794</v>
+        <v>6254919</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -2252,9 +2252,19 @@
           <t>2025-10-31</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,32 +2291,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129501845</v>
+        <v>129499979</v>
       </c>
       <c r="B16" t="n">
-        <v>58100</v>
+        <v>57895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466512</v>
+        <v>466402</v>
       </c>
       <c r="R16" t="n">
-        <v>6254919</v>
+        <v>6254794</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -2349,19 +2359,9 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,7 +2391,7 @@
         <v>129500120</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -2187,7 +2187,7 @@
         <v>129501845</v>
       </c>
       <c r="B15" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>129499979</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>129500120</v>
       </c>
       <c r="B17" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -2184,32 +2184,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129501845</v>
+        <v>129499979</v>
       </c>
       <c r="B15" t="n">
-        <v>58106</v>
+        <v>57896</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466512</v>
+        <v>466402</v>
       </c>
       <c r="R15" t="n">
-        <v>6254919</v>
+        <v>6254794</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -2252,19 +2252,9 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,32 +2281,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129499979</v>
+        <v>129501845</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>58106</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2326,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466402</v>
+        <v>466512</v>
       </c>
       <c r="R16" t="n">
-        <v>6254794</v>
+        <v>6254919</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -2359,9 +2349,19 @@
           <t>2025-10-31</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -2184,32 +2184,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129499979</v>
+        <v>129501845</v>
       </c>
       <c r="B15" t="n">
-        <v>57896</v>
+        <v>58106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466402</v>
+        <v>466512</v>
       </c>
       <c r="R15" t="n">
-        <v>6254794</v>
+        <v>6254919</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -2252,9 +2252,19 @@
           <t>2025-10-31</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,32 +2291,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129501845</v>
+        <v>129499979</v>
       </c>
       <c r="B16" t="n">
-        <v>58106</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466512</v>
+        <v>466402</v>
       </c>
       <c r="R16" t="n">
-        <v>6254919</v>
+        <v>6254794</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -2349,19 +2359,9 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -804,53 +804,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128259</v>
+        <v>127030122</v>
       </c>
       <c r="B3" t="n">
-        <v>58042</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fulagylet, Sk</t>
+          <t>Ost Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466457</v>
+        <v>466480</v>
       </c>
       <c r="R3" t="n">
-        <v>6255059</v>
+        <v>6254981</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -882,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,27 +923,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128256</v>
+        <v>127128259</v>
       </c>
       <c r="B4" t="n">
-        <v>57830</v>
+        <v>58027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,7 +953,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1034,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127829735</v>
+        <v>127128256</v>
       </c>
       <c r="B5" t="n">
-        <v>57845</v>
+        <v>57815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,26 +1049,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1077,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466358</v>
+        <v>466457</v>
       </c>
       <c r="R5" t="n">
-        <v>6254965</v>
+        <v>6255059</v>
       </c>
       <c r="S5" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,22 +1111,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127826639</v>
+        <v>127829735</v>
       </c>
       <c r="B6" t="n">
         <v>57845</v>
@@ -1179,7 +1183,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1188,17 +1192,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gripsvalla, Sk</t>
+          <t>Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466524</v>
+        <v>466358</v>
       </c>
       <c r="R6" t="n">
-        <v>6255148</v>
+        <v>6254965</v>
       </c>
       <c r="S6" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1241,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,39 +1261,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127829736</v>
+        <v>127826639</v>
       </c>
       <c r="B7" t="n">
-        <v>58055</v>
+        <v>57845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1303,17 +1307,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fulagylet, Sk</t>
+          <t>Gripsvalla, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466358</v>
+        <v>466524</v>
       </c>
       <c r="R7" t="n">
-        <v>6254965</v>
+        <v>6255148</v>
       </c>
       <c r="S7" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,14 +1376,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Per Muhr, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127831102</v>
+        <v>127829736</v>
       </c>
       <c r="B8" t="n">
         <v>58055</v>
@@ -1409,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1422,13 +1426,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466533</v>
+        <v>466358</v>
       </c>
       <c r="R8" t="n">
-        <v>6254716</v>
+        <v>6254965</v>
       </c>
       <c r="S8" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,17 +1491,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127826645</v>
+        <v>127831102</v>
       </c>
       <c r="B9" t="n">
-        <v>96173</v>
+        <v>58055</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,38 +1509,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gripsvalla, Sk</t>
+          <t>Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466524</v>
+        <v>466533</v>
       </c>
       <c r="R9" t="n">
-        <v>6255148</v>
+        <v>6254716</v>
       </c>
       <c r="S9" t="n">
         <v>59</v>
@@ -1568,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,42 +1613,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127826634</v>
+        <v>127826645</v>
       </c>
       <c r="B10" t="n">
-        <v>57682</v>
+        <v>96173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1720,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127831101</v>
+        <v>127826634</v>
       </c>
       <c r="B11" t="n">
-        <v>57843</v>
+        <v>57682</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,16 +1735,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1759,14 +1763,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fulagylet, Sk</t>
+          <t>Gripsvalla, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466533</v>
+        <v>466524</v>
       </c>
       <c r="R11" t="n">
-        <v>6254716</v>
+        <v>6255148</v>
       </c>
       <c r="S11" t="n">
         <v>59</v>
@@ -1798,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,27 +1839,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127826642</v>
+        <v>127831101</v>
       </c>
       <c r="B12" t="n">
-        <v>58055</v>
+        <v>57843</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1874,14 +1878,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gripsvalla, Sk</t>
+          <t>Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466524</v>
+        <v>466533</v>
       </c>
       <c r="R12" t="n">
-        <v>6255148</v>
+        <v>6254716</v>
       </c>
       <c r="S12" t="n">
         <v>59</v>
@@ -1913,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1927,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,60 +1954,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127030122</v>
+        <v>127826642</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>58055</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ost Fulagylet, Sk</t>
+          <t>Gripsvalla, Sk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466480</v>
+        <v>466524</v>
       </c>
       <c r="R13" t="n">
-        <v>6254981</v>
+        <v>6255148</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2027,22 +2027,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Per Muhr, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,6 +2483,219 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133659380</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58117</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fulagylet, Fulagylet, Sk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>466480</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6254894</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133658062</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fulagylet, Fulagylet, Sk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>466480</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6254894</v>
+      </c>
+      <c r="S19" t="n">
+        <v>100</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Örkened</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -2488,7 +2488,7 @@
         <v>133659380</v>
       </c>
       <c r="B18" t="n">
-        <v>58117</v>
+        <v>58124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>133658062</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -2488,7 +2488,7 @@
         <v>133659380</v>
       </c>
       <c r="B18" t="n">
-        <v>58124</v>
+        <v>58134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>133658062</v>
       </c>
       <c r="B19" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 34184-2025 artfynd.xlsx
+++ b/artfynd/A 34184-2025 artfynd.xlsx
@@ -675,65 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99029905</v>
+        <v>127826645</v>
       </c>
       <c r="B2" t="n">
-        <v>57193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lv 119, Sk</t>
+          <t>Gripsvalla, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466520.9223524028</v>
+        <v>466524</v>
       </c>
       <c r="R2" t="n">
-        <v>6254701.46952322</v>
+        <v>6255148</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,27 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-03-08</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-03-08</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>22:02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På Lv 119 framför bilen. I vinterdräkt.</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Robert Franzén</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Robert Franzén</t>
+          <t>Thomas Arnström, Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128259</v>
+        <v>127826634</v>
       </c>
       <c r="B3" t="n">
-        <v>58042</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,17 +825,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fulagylet, Sk</t>
+          <t>Gripsvalla, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466457</v>
+        <v>466524</v>
       </c>
       <c r="R3" t="n">
-        <v>6255059</v>
+        <v>6255148</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +859,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,34 +894,34 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Per Muhr, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128256</v>
+        <v>129500120</v>
       </c>
       <c r="B4" t="n">
-        <v>57830</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,28 +929,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fulagylet, Sk</t>
+          <t>Fulagylet, Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466457</v>
+        <v>466442</v>
       </c>
       <c r="R4" t="n">
-        <v>6255059</v>
+        <v>6254782</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,68 +986,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127829735</v>
+        <v>133658062</v>
       </c>
       <c r="B5" t="n">
-        <v>57845</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fulagylet, Sk</t>
+          <t>Fulagylet, Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466358</v>
+        <v>466480</v>
       </c>
       <c r="R5" t="n">
-        <v>6254965</v>
+        <v>6254894</v>
       </c>
       <c r="S5" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,22 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:05</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,49 +1083,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127826639</v>
+        <v>127128259</v>
       </c>
       <c r="B6" t="n">
-        <v>57845</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1188,17 +1134,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gripsvalla, Sk</t>
+          <t>Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466524</v>
+        <v>466457</v>
       </c>
       <c r="R6" t="n">
-        <v>6255148</v>
+        <v>6255059</v>
       </c>
       <c r="S6" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,17 +1203,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127829736</v>
+        <v>127826642</v>
       </c>
       <c r="B7" t="n">
-        <v>58055</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,17 +1249,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fulagylet, Sk</t>
+          <t>Gripsvalla, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466358</v>
+        <v>466524</v>
       </c>
       <c r="R7" t="n">
-        <v>6254965</v>
+        <v>6255148</v>
       </c>
       <c r="S7" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,17 +1318,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström, Per Muhr</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127831102</v>
+        <v>127829736</v>
       </c>
       <c r="B8" t="n">
-        <v>58055</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1355,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1422,13 +1368,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466533</v>
+        <v>466358</v>
       </c>
       <c r="R8" t="n">
-        <v>6254716</v>
+        <v>6254965</v>
       </c>
       <c r="S8" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,7 +1403,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1413,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,17 +1433,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127826645</v>
+        <v>127831102</v>
       </c>
       <c r="B9" t="n">
-        <v>96173</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,38 +1451,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gripsvalla, Sk</t>
+          <t>Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466524</v>
+        <v>466533</v>
       </c>
       <c r="R9" t="n">
-        <v>6255148</v>
+        <v>6254716</v>
       </c>
       <c r="S9" t="n">
         <v>59</v>
@@ -1568,7 +1518,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1528,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,27 +1555,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127826634</v>
+        <v>129501845</v>
       </c>
       <c r="B10" t="n">
-        <v>57682</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1633,28 +1583,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gripsvalla, Sk</t>
+          <t>Fulagylet, Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466524</v>
+        <v>466512</v>
       </c>
       <c r="R10" t="n">
-        <v>6255148</v>
+        <v>6254919</v>
       </c>
       <c r="S10" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,22 +1620,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,22 +1650,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127831101</v>
+        <v>127128256</v>
       </c>
       <c r="B11" t="n">
-        <v>57843</v>
+        <v>58112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,13 +1705,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466533</v>
+        <v>466457</v>
       </c>
       <c r="R11" t="n">
-        <v>6254716</v>
+        <v>6255059</v>
       </c>
       <c r="S11" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,22 +1735,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,34 +1770,34 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127826642</v>
+        <v>127831101</v>
       </c>
       <c r="B12" t="n">
-        <v>58055</v>
+        <v>58112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1874,14 +1816,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gripsvalla, Sk</t>
+          <t>Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466524</v>
+        <v>466533</v>
       </c>
       <c r="R12" t="n">
-        <v>6255148</v>
+        <v>6254716</v>
       </c>
       <c r="S12" t="n">
         <v>59</v>
@@ -1913,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1865,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127030122</v>
+        <v>128043396</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>58112</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,49 +1903,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ost Fulagylet, Sk</t>
+          <t>Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466480</v>
+        <v>466575</v>
       </c>
       <c r="R13" t="n">
-        <v>6254981</v>
+        <v>6254862</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2027,22 +1965,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,17 +2000,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Per Muhr, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128043396</v>
+        <v>133659380</v>
       </c>
       <c r="B14" t="n">
-        <v>57847</v>
+        <v>58134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2102,23 +2040,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fulagylet, Sk</t>
+          <t>Fulagylet, Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466575</v>
+        <v>466480</v>
       </c>
       <c r="R14" t="n">
-        <v>6254862</v>
+        <v>6254894</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2142,22 +2081,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,22 +2111,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129499979</v>
+        <v>127030122</v>
       </c>
       <c r="B15" t="n">
-        <v>57896</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,20 +2151,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fulagylet, Fulagylet, Sk</t>
+          <t>Ost Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466402</v>
+        <v>466480</v>
       </c>
       <c r="R15" t="n">
-        <v>6254794</v>
+        <v>6254981</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2249,12 +2200,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,60 +2230,68 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129501845</v>
+        <v>127826639</v>
       </c>
       <c r="B16" t="n">
-        <v>58106</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fulagylet, Fulagylet, Sk</t>
+          <t>Gripsvalla, Sk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466512</v>
+        <v>466524</v>
       </c>
       <c r="R16" t="n">
-        <v>6254919</v>
+        <v>6255148</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2346,22 +2315,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,22 +2345,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Thomas Arnström, Per Muhr</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129500120</v>
+        <v>127829735</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2399,37 +2368,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fulagylet, Fulagylet, Sk</t>
+          <t>Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466442</v>
+        <v>466358</v>
       </c>
       <c r="R17" t="n">
-        <v>6254782</v>
+        <v>6254965</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2453,12 +2430,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2473,22 +2460,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133659380</v>
+        <v>129499979</v>
       </c>
       <c r="B18" t="n">
-        <v>58134</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2496,46 +2483,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fulagylet, Fulagylet, Sk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466480</v>
+        <v>466402</v>
       </c>
       <c r="R18" t="n">
-        <v>6254894</v>
+        <v>6254794</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,22 +2537,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133658062</v>
+        <v>99029905</v>
       </c>
       <c r="B19" t="n">
-        <v>57972</v>
+        <v>56522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,37 +2580,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fulagylet, Fulagylet, Sk</t>
+          <t>Lv 119, Sk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466480</v>
+        <v>466521</v>
       </c>
       <c r="R19" t="n">
-        <v>6254894</v>
+        <v>6254701</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2666,12 +2646,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2022-03-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2022-03-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På Lv 119 framför bilen. I vinterdräkt.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,12 +2681,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Robert Franzén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Kornhall</t>
+          <t>Robert Franzén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
